--- a/Result/profitability/1736.xlsx
+++ b/Result/profitability/1736.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>2.10875</v>
+        <v>2.31125</v>
       </c>
       <c r="N2" t="n">
-        <v>50.50375</v>
+        <v>51.91249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8225</v>
+        <v>1.47875</v>
       </c>
       <c r="N3" t="n">
-        <v>50.42125</v>
+        <v>51.94625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.63</v>
       </c>
       <c r="M4" t="n">
-        <v>1.28375</v>
+        <v>1.56875</v>
       </c>
       <c r="N4" t="n">
-        <v>49.95124999999999</v>
+        <v>51.21625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.1</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0325</v>
+        <v>1.385</v>
       </c>
       <c r="N5" t="n">
-        <v>48.17875</v>
+        <v>49.685</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.9399999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.86875</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>48.18625</v>
+        <v>49.58125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.99</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4775</v>
+        <v>0.17</v>
       </c>
       <c r="N7" t="n">
-        <v>47.34249999999999</v>
+        <v>49.1225</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,16 +1391,16 @@
         <v>0.79</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.13</v>
+        <v>0.25875</v>
       </c>
       <c r="N8" t="n">
-        <v>46.61125</v>
+        <v>48.0475</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>-0.21625</v>
       </c>
       <c r="N12" t="n">
-        <v>45.35375</v>
+        <v>45.35375000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.11375</v>
       </c>
       <c r="N13" t="n">
-        <v>45.97749999999999</v>
+        <v>45.9775</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1736</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13267</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4932</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8335</v>
+      </c>
+      <c r="F75" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1972</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.86%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-615</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1357</v>
+      </c>
+      <c r="K75" t="n">
+        <v>969</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.48125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>52.50375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>38.875</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.223845704266511</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>7.621621621621621</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2373448887138072</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
